--- a/datos_centros.xlsx
+++ b/datos_centros.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://esbersl-my.sharepoint.com/personal/tecnico3_esbersl_com/Documents/Escritorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{D0239837-0E5F-4E37-AAB0-26B32C842CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{C5958592-9DE1-4A22-B5F5-99C20943FDD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{57B1429C-D6FC-444C-A642-B6BA357BD229}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>cliente</t>
   </si>
@@ -62,58 +62,28 @@
     <t>nif</t>
   </si>
   <si>
-    <t>Torrente</t>
-  </si>
-  <si>
     <t>Valencia</t>
   </si>
   <si>
     <t>provincia</t>
   </si>
   <si>
-    <t>BT01 - Pabellón Anabel Medina</t>
-  </si>
-  <si>
-    <t>BT02 - Pabellón Toll l'Alberca</t>
-  </si>
-  <si>
-    <t>BT03 - Parque Central (Parking)</t>
-  </si>
-  <si>
-    <t>BT04 - Piscina Municipal Vedat</t>
-  </si>
-  <si>
-    <t>BT05 - Pabellón El Vedat</t>
-  </si>
-  <si>
-    <t>BT06 - Piscina La Cotxera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C/. Ermiteta, 2 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">C/. Toll L’Alberca, Calle B, 49 </t>
-  </si>
-  <si>
-    <t>Avinguda Rei Joan Carles I, 22</t>
-  </si>
-  <si>
-    <t>Camino Romeral s/n</t>
-  </si>
-  <si>
-    <t>C/. El Sol, 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C/. Plà, 7 </t>
-  </si>
-  <si>
-    <t>FDM Torrent</t>
-  </si>
-  <si>
-    <t>P4600051-I</t>
-  </si>
-  <si>
-    <t>gallegoz@torrent.es</t>
+    <t>Torrent</t>
+  </si>
+  <si>
+    <t>BT01 - Pinturas Blatem</t>
+  </si>
+  <si>
+    <t>Crta. Masia del Juez, 36</t>
+  </si>
+  <si>
+    <t>Blatem</t>
+  </si>
+  <si>
+    <t>mantenimiento@blatem.com</t>
+  </si>
+  <si>
+    <t>B-46157533</t>
   </si>
 </sst>
 </file>
@@ -425,7 +395,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -476,6 +446,10 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -819,6 +793,7 @@
     <col min="3" max="3" width="15.5703125" customWidth="1"/>
     <col min="4" max="4" width="21.5703125" customWidth="1"/>
     <col min="7" max="7" width="31.42578125" customWidth="1"/>
+    <col min="8" max="8" width="19.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -847,184 +822,74 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="28" t="s">
         <v>11</v>
       </c>
       <c r="B2" s="30" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="D2" s="32" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E2">
         <v>46900</v>
       </c>
       <c r="F2">
-        <v>654210862</v>
+        <v>636681519</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="H2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="I2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3">
-        <v>46900</v>
-      </c>
-      <c r="F3">
-        <v>654210862</v>
-      </c>
-      <c r="G3" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4">
-        <v>46900</v>
-      </c>
-      <c r="F4">
-        <v>654210862</v>
-      </c>
-      <c r="G4" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="34">
-        <v>46900</v>
-      </c>
-      <c r="F5">
-        <v>654210862</v>
-      </c>
-      <c r="G5" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6">
-        <v>46900</v>
-      </c>
-      <c r="F6">
-        <v>654210862</v>
-      </c>
-      <c r="G6" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6" t="s">
-        <v>24</v>
-      </c>
-      <c r="I6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7">
-        <v>46900</v>
-      </c>
-      <c r="F7">
-        <v>654210862</v>
-      </c>
-      <c r="G7" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="H7" t="s">
-        <v>24</v>
-      </c>
-      <c r="I7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="9"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="8"/>
+      <c r="G3" s="20"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="12"/>
+      <c r="B4" s="13"/>
+      <c r="D4" s="11"/>
+      <c r="G4" s="20"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="9"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="34"/>
+      <c r="G5" s="20"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="12"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="11"/>
+      <c r="G6" s="20"/>
+    </row>
+    <row r="7" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="35"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="37"/>
+      <c r="D7" s="24"/>
+      <c r="G7" s="20"/>
+    </row>
+    <row r="8" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12"/>
       <c r="B8" s="13"/>
       <c r="C8" s="2"/>
